--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\سيستم تحديث مدفوعات الفواتير\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B378D3-BEAB-4DB0-84BE-C576171E5442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60ECAD08-9793-4ACC-BC3C-AEABDCED2CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{C69E70FF-C5F2-44DF-B4F9-1E4AE1B6936C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>Account No.</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Invoice_April_2026</t>
+  </si>
+  <si>
+    <t>system</t>
   </si>
 </sst>
 </file>
@@ -411,19 +414,6 @@
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF632423"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF632423"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF632423"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
         <color rgb="FF953734"/>
       </left>
       <right style="thick">
@@ -496,11 +486,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF632423"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -526,25 +525,22 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -553,8 +549,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -562,7 +567,13 @@
     <xf numFmtId="4" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -879,18 +890,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D881C7F-FF9E-4B77-B676-713E1A1096B7}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.1015625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.41796875" customWidth="1"/>
-    <col min="4" max="4" width="33.15625" customWidth="1"/>
-    <col min="5" max="5" width="17.734375" customWidth="1"/>
-    <col min="6" max="6" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="33.15625" customWidth="1"/>
+    <col min="6" max="6" width="17.734375" customWidth="1"/>
+    <col min="7" max="7" width="11" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="20.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,14 +914,17 @@
       <c r="D1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20.7" thickBot="1" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:7" ht="20.7" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A2" s="5">
         <v>6.1335309999999996</v>
       </c>
@@ -923,14 +937,17 @@
       <c r="D2" s="8">
         <v>101722.75</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="23">
+        <v>28929.75</v>
+      </c>
+      <c r="F2" s="21">
         <v>23379.75</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="G2" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
@@ -943,14 +960,17 @@
       <c r="D3" s="8">
         <v>76567.16</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="23">
         <v>33670</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F3" s="21">
+        <v>33670</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -963,14 +983,17 @@
       <c r="D4" s="8">
         <v>84700.04</v>
       </c>
-      <c r="E4" s="20">
-        <v>0</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E4" s="23">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
@@ -983,14 +1006,17 @@
       <c r="D5" s="8">
         <v>70934.149999999994</v>
       </c>
-      <c r="E5" s="20">
-        <v>0</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E5" s="23">
+        <v>0</v>
+      </c>
+      <c r="F5" s="22">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -1003,14 +1029,17 @@
       <c r="D6" s="8">
         <v>41159.21</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="23">
         <v>-1800</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F6" s="22">
+        <v>-1800</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
@@ -1023,14 +1052,17 @@
       <c r="D7" s="8">
         <v>331849.58</v>
       </c>
-      <c r="E7" s="19">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E7" s="23">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
@@ -1040,17 +1072,20 @@
       <c r="C8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20">
+      <c r="D8" s="20">
+        <v>0</v>
+      </c>
+      <c r="E8" s="24">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22">
         <v>101669.95</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -1063,14 +1098,17 @@
       <c r="D9" s="8">
         <v>160348.81</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="23">
         <v>33998.81</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F9" s="21">
+        <v>33998.81</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
@@ -1083,14 +1121,17 @@
       <c r="D10" s="8">
         <v>4040.54</v>
       </c>
-      <c r="E10" s="20">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E10" s="23">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
@@ -1100,17 +1141,20 @@
       <c r="C11" s="7">
         <v>1155666925</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>-867.39</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="25">
         <v>-1462.39</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F11" s="22">
+        <v>-1462.39</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
@@ -1123,14 +1167,17 @@
       <c r="D12" s="8">
         <v>16839.79</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="23">
         <v>20.350000000000001</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F12" s="21">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A13" s="9" t="s">
         <v>23</v>
       </c>
@@ -1143,14 +1190,17 @@
       <c r="D13" s="8">
         <v>164681.32999999999</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="23">
         <v>50574.13</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F13" s="21">
+        <v>50574.13</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
@@ -1163,14 +1213,17 @@
       <c r="D14" s="8">
         <v>46269.18</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="23">
         <v>-200</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F14" s="22">
+        <v>-200</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
@@ -1183,14 +1236,17 @@
       <c r="D15" s="8">
         <v>80590.7</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="23">
         <v>47438.82</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F15" s="21">
+        <v>47438.82</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A16" s="9" t="s">
         <v>29</v>
       </c>
@@ -1203,18 +1259,21 @@
       <c r="D16" s="8">
         <v>9645.2199999999993</v>
       </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E16" s="23">
+        <v>0</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="7">
@@ -1223,14 +1282,17 @@
       <c r="D17" s="8">
         <v>0</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="23">
         <v>21473.599999999999</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F17" s="21">
+        <v>21473.599999999999</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A18" s="9" t="s">
         <v>33</v>
       </c>
@@ -1243,14 +1305,17 @@
       <c r="D18" s="8">
         <v>171360.4</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="23">
         <v>24079</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F18" s="21">
+        <v>24079</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A19" s="9" t="s">
         <v>35</v>
       </c>
@@ -1263,18 +1328,21 @@
       <c r="D19" s="8">
         <v>65893.64</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="23">
         <v>-6036.11</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F19" s="22">
+        <v>-6036.11</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="7">
@@ -1283,18 +1351,21 @@
       <c r="D20" s="8">
         <v>75351.199999999997</v>
       </c>
-      <c r="E20" s="19">
-        <v>0</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E20" s="23">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A21" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="7">
@@ -1303,18 +1374,21 @@
       <c r="D21" s="8">
         <v>55936.07</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="23">
         <v>18281</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F21" s="21">
+        <v>18281</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="7">
@@ -1323,18 +1397,21 @@
       <c r="D22" s="8">
         <v>60868.07</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="23">
         <v>35615.410000000003</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F22" s="21">
+        <v>35615.410000000003</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A23" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="7">
@@ -1343,18 +1420,21 @@
       <c r="D23" s="8">
         <v>46776.87</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="23">
         <v>-1146</v>
       </c>
-      <c r="F23" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F23" s="22">
+        <v>-1146</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A24" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C24" s="7">
@@ -1363,18 +1443,21 @@
       <c r="D24" s="8">
         <v>64083.71</v>
       </c>
-      <c r="E24" s="19">
-        <v>0</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E24" s="23">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A25" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="7">
@@ -1383,18 +1466,21 @@
       <c r="D25" s="8">
         <v>307.49</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="23">
         <v>-30</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F25" s="22">
+        <v>-30</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A26" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="7">
@@ -1403,18 +1489,21 @@
       <c r="D26" s="8">
         <v>36634.33</v>
       </c>
-      <c r="E26" s="19">
-        <v>0</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="E26" s="23">
+        <v>0</v>
+      </c>
+      <c r="F26" s="21">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A27" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="7">
@@ -1423,18 +1512,21 @@
       <c r="D27" s="8">
         <v>20005.580000000002</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="23">
         <v>-9670</v>
       </c>
-      <c r="F27" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F27" s="22">
+        <v>-9670</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A28" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C28" s="7">
@@ -1443,18 +1535,21 @@
       <c r="D28" s="8">
         <v>43.73</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="23">
         <v>-0.27</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="F28" s="21">
+        <v>-0.27</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A29" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C29" s="7">
@@ -1463,16 +1558,19 @@
       <c r="D29" s="8">
         <v>43.73</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="23">
         <v>-0.27</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="F29" s="21">
+        <v>-0.27</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="36" spans="3:3" ht="19.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="C36" s="16"/>
+      <c r="C36" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
